--- a/plantilla_inicio_finanzas.xlsx
+++ b/plantilla_inicio_finanzas.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Empezar aqui" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="222">
   <si>
     <t xml:space="preserve">Empezar de nuevo, bien</t>
   </si>
@@ -126,6 +126,9 @@
     <t xml:space="preserve">Tu nombre</t>
   </si>
   <si>
+    <t xml:space="preserve">Jordan</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sale en el estado de cuenta mensual.</t>
   </si>
   <si>
@@ -198,7 +201,7 @@
     <t xml:space="preserve">Cuenta donde cae el sueldo</t>
   </si>
   <si>
-    <t xml:space="preserve">Cuenta bancaria BCP</t>
+    <t xml:space="preserve">Cuenta Sueldo BCP</t>
   </si>
   <si>
     <t xml:space="preserve">Escribela igual que en la hoja 2 Cuentas.</t>
@@ -237,10 +240,25 @@
     <t xml:space="preserve">Efectivo</t>
   </si>
   <si>
-    <t xml:space="preserve">Yape / Plin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debito BCP</t>
+    <t xml:space="preserve">Emergencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuenta BCP / Yape </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compras </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sueldo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wardadito BCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahorro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuenta Interbank / Plin </t>
   </si>
   <si>
     <t xml:space="preserve">Caja Huancayo</t>
@@ -333,7 +351,10 @@
     <t xml:space="preserve">Cuota mensual (calculada)</t>
   </si>
   <si>
-    <t xml:space="preserve">Celular en 12 cuotas</t>
+    <t xml:space="preserve">General - inicio 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General - inicio 2</t>
   </si>
   <si>
     <t xml:space="preserve">Total deuda en cuotas</t>
@@ -372,6 +393,12 @@
     <t xml:space="preserve">Prestamo Caja Huancayo</t>
   </si>
   <si>
+    <t xml:space="preserve">Prestamo BCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prestamo Ripley</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total que debes</t>
   </si>
   <si>
@@ -402,22 +429,31 @@
     <t xml:space="preserve">De que cuenta sale</t>
   </si>
   <si>
-    <t xml:space="preserve">Plan de celular</t>
+    <t xml:space="preserve">iCloud</t>
   </si>
   <si>
     <t xml:space="preserve">Servicios (luz, agua, internet, cel)</t>
   </si>
   <si>
-    <t xml:space="preserve">Internet</t>
+    <t xml:space="preserve">Claro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Movistar</t>
   </si>
   <si>
     <t xml:space="preserve">Total fijo al mes</t>
   </si>
   <si>
-    <t xml:space="preserve">Las dos filas en gris son ejemplos: cambialas por las tuyas reales o borralas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Van aqui: celular, internet, luz, agua, streaming, gym, alquiler. No pongas las cuotas de tarjeta ni los prestamos, esos ya estan en las hojas 4 y 5.</t>
+    <t xml:space="preserve">Sale de tu Excel de gastos (GASTO FIJO): iCloud 45, Claro 50, Movistar 80. Total 175 al mes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo que yo puse a ojo y tienes que corregir: el dia de cobro de cada uno (5, 10 y 15) y que los tres salgan de la Cuenta Sueldo BCP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El 'BCP 260' de tu Excel no esta aqui: es el prestamo BCP de 266.42 que ya pusiste en la hoja 5. Ponerlo dos veces te duplicaria el gasto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No pongas aqui las cuotas de tarjeta ni los prestamos: ya estan en las hojas 4 y 5.</t>
   </si>
   <si>
     <t xml:space="preserve">7. Cuanto quieres gastar al mes</t>
@@ -441,48 +477,84 @@
     <t xml:space="preserve">Necesidad</t>
   </si>
   <si>
+    <t xml:space="preserve">Tu Excel: 750 al mes todo 2027 (25 al dia).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Transporte</t>
   </si>
   <si>
+    <t xml:space="preserve">Tu Excel: 150 al mes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iCloud 45 + Claro 50 + Movistar 80, igual que la hoja 6.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vivienda / Alquiler</t>
   </si>
   <si>
+    <t xml:space="preserve">No tienes alquiler en tu Excel.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Salud</t>
   </si>
   <si>
+    <t xml:space="preserve">Tu Excel no tiene nada de salud. Si gastas en farmacia, ponle un limite.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pago de deudas</t>
   </si>
   <si>
     <t xml:space="preserve">Deuda</t>
   </si>
   <si>
+    <t xml:space="preserve">Dejalo en cero: la app lo pone sola igual a las cuotas del mes.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gym / Deporte</t>
   </si>
   <si>
     <t xml:space="preserve">Gusto</t>
   </si>
   <si>
+    <t xml:space="preserve">Tu Excel: 200 al mes desde enero 2027 (en 2026 estaba en cero).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Restaurantes / Salidas</t>
   </si>
   <si>
+    <t xml:space="preserve">Tu Excel no lo separa. Si quieres verlo aparte, sacale plata a Alimentacion u Otros.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Entretenimiento</t>
   </si>
   <si>
+    <t xml:space="preserve">Tu Excel no lo tiene. Streaming y salidas estan dentro de Otros.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ropa</t>
   </si>
   <si>
+    <t xml:space="preserve">Tu Excel: 300 cada dos meses = 150 al mes en promedio. Si prefieres que no te marque exceso el mes que compras, sube a 300.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Otros</t>
   </si>
   <si>
+    <t xml:space="preserve">Tu Excel: 300 al mes.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ahorro / Fondo</t>
   </si>
   <si>
-    <t xml:space="preserve">Ahorro</t>
+    <t xml:space="preserve">En cero a proposito: con tus cuotas de hoy no sobra para ahorrar.</t>
   </si>
   <si>
     <t xml:space="preserve">Aporte a metas</t>
   </si>
   <si>
+    <t xml:space="preserve">En cero por lo mismo.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total asignado</t>
   </si>
   <si>
@@ -516,6 +588,78 @@
     <t xml:space="preserve">Pago de deudas no necesita limite: la app lo pone sola igual a las cuotas del mes.</t>
   </si>
   <si>
+    <t xml:space="preserve">Lo que entra y lo que sale, con tus numeros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo que te cae al mes (tus dos quincenas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De la hoja 1. Es la plata que entra de verdad a tu cuenta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo que cuesta vivir al mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El total de limites de arriba.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuotas de tarjeta de octubre 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las cuatro compras de la hoja 4 arrancan en octubre, asi que todas caen este mes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuotas de prestamos al mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los cinco prestamos de la hoja 5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total a pagar en octubre 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vivir + tarjetas + prestamos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te falta en octubre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En rojo = lo que tendrias que sacar de tus cuentas o de la Caja Huancayo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total a pagar desde enero 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En enero ya no quedan cuotas de tarjeta: solo prestamos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te falta cada mes desde enero 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Este es el hueco de fondo, el que no se arregla solo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grati + CTS + bono, repartido por mes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De tu Excel 2027: grati 3500 x2, CTS 1750 x2, bono 3500 = 14,000 al ano.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te falta desde enero contando grati, CTS y bono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asi queda el ano si usas toda la grati y la CTS en tapar el hueco.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los montos de arriba salen de tu Excel 'Finanzas_personal_1', hoja General, plan 2027.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ojo con tres cifras de ingreso que no coinciden: tus quincenas suman 2,969.94, la formula de AFP da 3,048.50 y tu Excel dice 3,000. Dime cual es la de tu boleta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grati, CTS y bono no van como ingreso fijo en la app porque no son mensuales: los anotas como Ingreso el mes que caen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">8. Para que estas ahorrando</t>
   </si>
   <si>
@@ -537,26 +681,33 @@
     <t xml:space="preserve">Fondo de emergencia</t>
   </si>
   <si>
-    <t xml:space="preserve">2027-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Borra la fila del ejemplo si no te sirve, o cambiala por tu meta real.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Si lo que tienes ya ahorrado esta en una de tus cuentas de la hoja 2, no pasa nada: la meta no mueve plata, solo lleva la cuenta.</t>
+    <t xml:space="preserve">2027-12-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Objetivo 5,175 = tres meses de lo que cuesta vivir segun la hoja 7 (1,725 x 3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ya ahorrado 9,500 = la Caja Huancayo que marcaste como Emergencia en la hoja 2. Estas por encima del objetivo, asi que la app la va a mostrar cumplida: sirve como el piso que no quieres bajar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No le puse mas metas a proposito: con lo que debes hoy, no hay de donde sacar para una meta nueva. Si quieres una igual, dime cual y la agrego.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Wardadito BCP de 1,200 lo dejaste en la hoja 2, asi que la app lo va a contar como disponible. Si no quieres verlo asi, avisame y lo saco.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="0"/>
+    <numFmt numFmtId="168" formatCode="#,##0.00;[RED]\-#,##0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -619,6 +770,14 @@
       <i val="true"/>
       <sz val="10"/>
       <color rgb="FF9AA0A6"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F4E45"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -705,7 +864,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -802,7 +961,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1059,7 +1242,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:B33"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="104"/>
@@ -1212,7 +1395,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
@@ -1244,153 +1427,161 @@
       <c r="A5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="9"/>
+      <c r="B5" s="9" t="s">
+        <v>32</v>
+      </c>
       <c r="C5" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="11"/>
+        <v>37</v>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>3500</v>
+      </c>
       <c r="C7" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>0.1</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>0.0155</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>0.0135</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="11" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12" s="11" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="11"/>
+        <v>52</v>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>1484.97</v>
+      </c>
       <c r="C14" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="11"/>
+        <v>54</v>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>1484.97</v>
+      </c>
       <c r="C15" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B18" s="14" t="n">
         <f aca="false">IFERROR(B7-(B7*(B8+B9+B10)+B11),0)</f>
-        <v>0</v>
+        <v>3048.5</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B19" s="14" t="n">
         <f aca="false">IFERROR(B18+B12,0)</f>
-        <v>0</v>
+        <v>3048.5</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1415,8 +1606,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C32"/>
+  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
@@ -1425,71 +1616,101 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="9"/>
+        <v>69</v>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>350</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="9"/>
+        <v>71</v>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>238.92</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="9"/>
+        <v>57</v>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>108.71</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="9"/>
+        <v>74</v>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="9"/>
+        <v>76</v>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>233.84</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>9500</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="9"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9"/>
@@ -1567,28 +1788,33 @@
       <c r="C26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" s="14" t="n">
-        <f aca="false">SUM(B5:B26)</f>
-        <v>0</v>
-      </c>
-      <c r="C27" s="16"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
-        <v>74</v>
-      </c>
+      <c r="A27" s="9"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="9"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="14" t="n">
+        <f aca="false">SUM(B5:B27)</f>
+        <v>11651.47</v>
+      </c>
+      <c r="C28" s="16"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1608,7 +1834,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
@@ -1620,57 +1846,69 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="17"/>
+        <v>91</v>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>10700</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>20</v>
+      </c>
       <c r="D5" s="17" t="n">
         <v>25</v>
       </c>
       <c r="E5" s="11"/>
-      <c r="F5" s="9"/>
+      <c r="F5" s="9" t="n">
+        <v>1973</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="17"/>
+        <v>92</v>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>3750</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>20</v>
+      </c>
       <c r="D6" s="17" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E6" s="11"/>
-      <c r="F6" s="9"/>
+      <c r="F6" s="9" t="n">
+        <v>141</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9"/>
@@ -1738,22 +1976,22 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1773,7 +2011,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -1787,52 +2025,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C5" s="19" t="n">
-        <v>1800</v>
+        <v>2750</v>
       </c>
       <c r="D5" s="20" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E5" s="21" t="n">
         <v>0</v>
@@ -1845,225 +2083,267 @@
       </c>
       <c r="H5" s="22" t="n">
         <f aca="false">IFERROR(IF(OR($C5="",$D5="",$D5=0),"",IF(N($E5)&gt;0,$C5*((1+$E5)^(1/12)-1)/(1-(1+((1+$E5)^(1/12)-1))^(-$D5)),$C5/$D5)),"")</f>
-        <v>200</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="22" t="str">
+      <c r="A6" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>4650</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="20" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H6" s="22" t="n">
         <f aca="false">IFERROR(IF(OR($C6="",$D6="",$D6=0),"",IF(N($E6)&gt;0,$C6*((1+$E6)^(1/12)-1)/(1-(1+((1+$E6)^(1/12)-1))^(-$D6)),$C6/$D6)),"")</f>
-        <v/>
+        <v>1550</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="22" t="str">
+      <c r="A7" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>413</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="20" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H7" s="22" t="n">
         <f aca="false">IFERROR(IF(OR($C7="",$D7="",$D7=0),"",IF(N($E7)&gt;0,$C7*((1+$E7)^(1/12)-1)/(1-(1+((1+$E7)^(1/12)-1))^(-$D7)),$C7/$D7)),"")</f>
-        <v/>
+        <v>413</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="22" t="str">
+      <c r="A8" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="20" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H8" s="22" t="n">
         <f aca="false">IFERROR(IF(OR($C8="",$D8="",$D8=0),"",IF(N($E8)&gt;0,$C8*((1+$E8)^(1/12)-1)/(1-(1+((1+$E8)^(1/12)-1))^(-$D8)),$C8/$D8)),"")</f>
-        <v/>
+        <v>1000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
       <c r="C9" s="11"/>
       <c r="D9" s="17"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
       <c r="H9" s="22" t="str">
         <f aca="false">IFERROR(IF(OR($C9="",$D9="",$D9=0),"",IF(N($E9)&gt;0,$C9*((1+$E9)^(1/12)-1)/(1-(1+((1+$E9)^(1/12)-1))^(-$D9)),$C9/$D9)),"")</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
       <c r="C10" s="11"/>
       <c r="D10" s="17"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
       <c r="H10" s="22" t="str">
         <f aca="false">IFERROR(IF(OR($C10="",$D10="",$D10=0),"",IF(N($E10)&gt;0,$C10*((1+$E10)^(1/12)-1)/(1-(1+((1+$E10)^(1/12)-1))^(-$D10)),$C10/$D10)),"")</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="11"/>
       <c r="D11" s="17"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
       <c r="H11" s="22" t="str">
         <f aca="false">IFERROR(IF(OR($C11="",$D11="",$D11=0),"",IF(N($E11)&gt;0,$C11*((1+$E11)^(1/12)-1)/(1-(1+((1+$E11)^(1/12)-1))^(-$D11)),$C11/$D11)),"")</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="11"/>
       <c r="D12" s="17"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
       <c r="H12" s="22" t="str">
         <f aca="false">IFERROR(IF(OR($C12="",$D12="",$D12=0),"",IF(N($E12)&gt;0,$C12*((1+$E12)^(1/12)-1)/(1-(1+((1+$E12)^(1/12)-1))^(-$D12)),$C12/$D12)),"")</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
       <c r="C13" s="11"/>
       <c r="D13" s="17"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
       <c r="H13" s="22" t="str">
         <f aca="false">IFERROR(IF(OR($C13="",$D13="",$D13=0),"",IF(N($E13)&gt;0,$C13*((1+$E13)^(1/12)-1)/(1-(1+((1+$E13)^(1/12)-1))^(-$D13)),$C13/$D13)),"")</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
       <c r="C14" s="11"/>
       <c r="D14" s="17"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
       <c r="H14" s="22" t="str">
         <f aca="false">IFERROR(IF(OR($C14="",$D14="",$D14=0),"",IF(N($E14)&gt;0,$C14*((1+$E14)^(1/12)-1)/(1-(1+((1+$E14)^(1/12)-1))^(-$D14)),$C14/$D14)),"")</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="11"/>
       <c r="D15" s="17"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
       <c r="H15" s="22" t="str">
         <f aca="false">IFERROR(IF(OR($C15="",$D15="",$D15=0),"",IF(N($E15)&gt;0,$C15*((1+$E15)^(1/12)-1)/(1-(1+((1+$E15)^(1/12)-1))^(-$D15)),$C15/$D15)),"")</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
       <c r="C16" s="11"/>
       <c r="D16" s="17"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
       <c r="H16" s="22" t="str">
         <f aca="false">IFERROR(IF(OR($C16="",$D16="",$D16=0),"",IF(N($E16)&gt;0,$C16*((1+$E16)^(1/12)-1)/(1-(1+((1+$E16)^(1/12)-1))^(-$D16)),$C16/$D16)),"")</f>
         <v/>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
       <c r="C17" s="11"/>
       <c r="D17" s="17"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
       <c r="H17" s="22" t="str">
         <f aca="false">IFERROR(IF(OR($C17="",$D17="",$D17=0),"",IF(N($E17)&gt;0,$C17*((1+$E17)^(1/12)-1)/(1-(1+((1+$E17)^(1/12)-1))^(-$D17)),$C17/$D17)),"")</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
       <c r="C18" s="11"/>
       <c r="D18" s="17"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
       <c r="H18" s="22" t="str">
         <f aca="false">IFERROR(IF(OR($C18="",$D18="",$D18=0),"",IF(N($E18)&gt;0,$C18*((1+$E18)^(1/12)-1)/(1-(1+((1+$E18)^(1/12)-1))^(-$D18)),$C18/$D18)),"")</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
       <c r="C19" s="11"/>
       <c r="D19" s="17"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
       <c r="H19" s="22" t="str">
         <f aca="false">IFERROR(IF(OR($C19="",$D19="",$D19=0),"",IF(N($E19)&gt;0,$C19*((1+$E19)^(1/12)-1)/(1-(1+((1+$E19)^(1/12)-1))^(-$D19)),$C19/$D19)),"")</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
       <c r="C20" s="11"/>
       <c r="D20" s="17"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
       <c r="H20" s="22" t="str">
         <f aca="false">IFERROR(IF(OR($C20="",$D20="",$D20=0),"",IF(N($E20)&gt;0,$C20*((1+$E20)^(1/12)-1)/(1-(1+((1+$E20)^(1/12)-1))^(-$D20)),$C20/$D20)),"")</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
       <c r="C21" s="11"/>
       <c r="D21" s="17"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
       <c r="H21" s="22" t="str">
         <f aca="false">IFERROR(IF(OR($C21="",$D21="",$D21=0),"",IF(N($E21)&gt;0,$C21*((1+$E21)^(1/12)-1)/(1-(1+((1+$E21)^(1/12)-1))^(-$D21)),$C21/$D21)),"")</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
       <c r="C22" s="11"/>
       <c r="D22" s="17"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
       <c r="H22" s="22" t="str">
         <f aca="false">IFERROR(IF(OR($C22="",$D22="",$D22=0),"",IF(N($E22)&gt;0,$C22*((1+$E22)^(1/12)-1)/(1-(1+((1+$E22)^(1/12)-1))^(-$D22)),$C22/$D22)),"")</f>
         <v/>
@@ -2123,12 +2403,12 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="14" t="n">
         <f aca="false">SUM(C5:C26)</f>
-        <v>1800</v>
+        <v>9813</v>
       </c>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
@@ -2136,41 +2416,35 @@
       <c r="G27" s="16"/>
       <c r="H27" s="14" t="n">
         <f aca="false">SUM(H5:H26)</f>
-        <v>200</v>
+        <v>5713</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="A5:A26" type="list">
-      <formula1>'3 Tarjetas'!$A$5:$A$14</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2187,7 +2461,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19"/>
@@ -2200,52 +2474,52 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B5" s="19" t="n">
-        <v>4200</v>
+        <v>20000</v>
       </c>
       <c r="C5" s="19" t="n">
-        <v>350</v>
+        <v>1200</v>
       </c>
       <c r="D5" s="20" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E5" s="20" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F5" s="20" t="n">
         <v>10</v>
@@ -2255,47 +2529,103 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
+      <c r="A6" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="19" t="n">
+        <v>11500</v>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>447.95</v>
+      </c>
+      <c r="D6" s="20" t="n">
+        <v>59</v>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="20" t="n">
+        <v>2026</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
+      <c r="A7" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>14500</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>534</v>
+      </c>
+      <c r="D7" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="20" t="n">
+        <v>2026</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
+      <c r="A8" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="19" t="n">
+        <v>2684.56</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>266.42</v>
+      </c>
+      <c r="D8" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="F8" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="20" t="n">
+        <v>2026</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
+      <c r="A9" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>210</v>
+      </c>
+      <c r="D9" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="20" t="n">
+        <v>2026</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
       <c r="F10" s="17"/>
       <c r="G10" s="17"/>
     </row>
@@ -2373,15 +2703,15 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B19" s="14" t="n">
         <f aca="false">SUM(B5:B18)</f>
-        <v>4200</v>
+        <v>49684.56</v>
       </c>
       <c r="C19" s="14" t="n">
         <f aca="false">SUM(C5:C18)</f>
-        <v>350</v>
+        <v>2658.37</v>
       </c>
       <c r="D19" s="16"/>
       <c r="E19" s="16"/>
@@ -2390,17 +2720,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -2419,8 +2749,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
@@ -2431,71 +2761,81 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="C5" s="19" t="n">
-        <v>60</v>
-      </c>
-      <c r="D5" s="20" t="n">
+      <c r="A5" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="D5" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="18" t="s">
-        <v>56</v>
+      <c r="E5" s="9" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6" s="19" t="n">
-        <v>90</v>
-      </c>
-      <c r="D6" s="20" t="n">
+      <c r="A6" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="E6" s="18" t="s">
-        <v>56</v>
+      <c r="E6" s="9" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="9"/>
+      <c r="A7" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9"/>
@@ -2632,37 +2972,37 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="14" t="n">
         <f aca="false">SUM(C5:C26)</f>
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B5:B26" type="list">
-      <formula1>'7 Presupuesto'!$A$5:$A$17</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E5:E26" type="list">
-      <formula1>'2 Cuentas'!$A$5:$A$26</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2678,266 +3018,292 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>500</v>
-      </c>
-      <c r="D5" s="9"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>750</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="D6" s="9"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D6" s="24" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>200</v>
-      </c>
-      <c r="D7" s="9"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>175</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="9"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D8" s="24" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="9"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D9" s="24" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="C10" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="9"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D10" s="24" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="9"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>200</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="C12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="9"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D12" s="24" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="C13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="9"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D13" s="24" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="9"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>150</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="9"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>300</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="C16" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="9"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D16" s="24" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="C17" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="9"/>
+      <c r="D17" s="24" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="B18" s="16"/>
       <c r="C18" s="14" t="n">
         <f aca="false">SUM(C5:C17)</f>
-        <v>850</v>
+        <v>1725</v>
       </c>
       <c r="D18" s="16"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24" t="s">
-        <v>152</v>
+      <c r="A20" s="25" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="B22" s="22" t="n">
         <f aca="false">IFERROR('1 Perfil'!$B$19*0.5,0)</f>
-        <v>0</v>
+        <v>1524.25</v>
       </c>
       <c r="C22" s="22" t="n">
         <f aca="false">SUMIF($B$5:$B$17,"Necesidad",$C$5:$C$17)</f>
-        <v>850</v>
+        <v>1075</v>
       </c>
       <c r="D22" s="22" t="n">
         <f aca="false">C22-B22</f>
-        <v>850</v>
+        <v>-449.25</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="B23" s="22" t="n">
         <f aca="false">IFERROR('1 Perfil'!$B$19*0.3,0)</f>
-        <v>0</v>
+        <v>914.55</v>
       </c>
       <c r="C23" s="22" t="n">
         <f aca="false">SUMIF($B$5:$B$17,"Gusto",$C$5:$C$17)</f>
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="D23" s="22" t="n">
         <f aca="false">C23-B23</f>
-        <v>0</v>
+        <v>-264.55</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="B24" s="22" t="n">
         <f aca="false">IFERROR('1 Perfil'!$B$19*0.2,0)</f>
-        <v>0</v>
+        <v>609.7</v>
       </c>
       <c r="C24" s="22" t="n">
         <f aca="false">SUMIF($B$5:$B$17,"Ahorro",$C$5:$C$17)+SUMIF($B$5:$B$17,"Deuda",$C$5:$C$17)</f>
@@ -2945,22 +3311,170 @@
       </c>
       <c r="D24" s="22" t="n">
         <f aca="false">C24-B24</f>
-        <v>0</v>
+        <v>-609.7</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>161</v>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="26" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="B32" s="22" t="n">
+        <f aca="false">'1 Perfil'!$B$14+'1 Perfil'!$B$15</f>
+        <v>2969.94</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="B33" s="22" t="n">
+        <f aca="false">$C$18</f>
+        <v>1725</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="B34" s="22" t="n">
+        <f aca="false">'4 Cuotas tarjeta'!$H$27</f>
+        <v>5713</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="B35" s="22" t="n">
+        <f aca="false">'5 Prestamos'!$C$19</f>
+        <v>2658.37</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="B36" s="29" t="n">
+        <f aca="false">B33+B34+B35</f>
+        <v>10096.37</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="B37" s="30" t="n">
+        <f aca="false">B32-B36</f>
+        <v>-7126.43</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="B38" s="29" t="n">
+        <f aca="false">B33+B35</f>
+        <v>4383.37</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="B39" s="30" t="n">
+        <f aca="false">B32-B38</f>
+        <v>-1413.43</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="B40" s="22" t="n">
+        <f aca="false">14000/12</f>
+        <v>1166.66666666667</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B41" s="30" t="n">
+        <f aca="false">B39+B40</f>
+        <v>-246.763333333333</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -2979,8 +3493,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18"/>
@@ -2989,40 +3503,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>162</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>163</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>164</v>
+        <v>212</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>165</v>
+        <v>213</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>166</v>
+        <v>214</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>167</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="B5" s="19" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C5" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>169</v>
+      <c r="A5" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>5175</v>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>9500</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3093,12 +3607,22 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>170</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>171</v>
+        <v>219</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/plantilla_inicio_finanzas.xlsx
+++ b/plantilla_inicio_finanzas.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="232">
   <si>
     <t xml:space="preserve">Empezar de nuevo, bien</t>
   </si>
@@ -219,7 +219,7 @@
     <t xml:space="preserve">Neto + otros ingresos. Sobre este numero se reparte el 50/30/20.</t>
   </si>
   <si>
-    <t xml:space="preserve">Si las dos quincenas no suman tu neto, no te preocupes: manda igual los dos numeros reales y yo cuadro la diferencia.</t>
+    <t xml:space="preserve">Tu neto real son 2,969.94 (tus dos quincenas). Con bruto 3,500 y la AFP al 12.9% salian 3,048.50, asi que los 78.56 que sobraban van como 'otros descuentos'. Si en tu boleta ves de que es ese descuento, dimelo y lo nombramos bien.</t>
   </si>
   <si>
     <t xml:space="preserve">2. Donde tienes plata hoy</t>
@@ -594,7 +594,7 @@
     <t xml:space="preserve">Lo que te cae al mes (tus dos quincenas)</t>
   </si>
   <si>
-    <t xml:space="preserve">De la hoja 1. Es la plata que entra de verdad a tu cuenta.</t>
+    <t xml:space="preserve">2,969.94. Es tu neto real, confirmado por ti.</t>
   </si>
   <si>
     <t xml:space="preserve">Lo que cuesta vivir al mes</t>
@@ -624,7 +624,31 @@
     <t xml:space="preserve">Te falta en octubre</t>
   </si>
   <si>
-    <t xml:space="preserve">En rojo = lo que tendrias que sacar de tus cuentas o de la Caja Huancayo.</t>
+    <t xml:space="preserve">Lo tendrias que sacar de tus cuentas o de la Caja Huancayo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuotas de tarjeta de noviembre 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las dos compras que siguen vivas: BCP 1,550 + Interbank 1,000. Puesto a mano, no sale de una formula.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viaje a Argentina (una sola vez)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo que falta del viaje. El pasaje de 2,500 ya lo pagaste, asi que no se cuenta otra vez.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total a pagar en noviembre 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vivir + tarjetas + prestamos + viaje.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te falta en noviembre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El mes mas caro de los dos.</t>
   </si>
   <si>
     <t xml:space="preserve">Total a pagar desde enero 2027</t>
@@ -636,28 +660,28 @@
     <t xml:space="preserve">Te falta cada mes desde enero 2027</t>
   </si>
   <si>
-    <t xml:space="preserve">Este es el hueco de fondo, el que no se arregla solo.</t>
+    <t xml:space="preserve">Este es el hueco de fondo, el que no se arregla solo hasta marzo de 2028.</t>
   </si>
   <si>
     <t xml:space="preserve">Grati + CTS + bono, repartido por mes</t>
   </si>
   <si>
-    <t xml:space="preserve">De tu Excel 2027: grati 3500 x2, CTS 1750 x2, bono 3500 = 14,000 al ano.</t>
+    <t xml:space="preserve">De tu Excel 2027: grati 3,500 x2, CTS 1,750 x2, bono 3,500 = 14,000 al ano.</t>
   </si>
   <si>
     <t xml:space="preserve">Te falta desde enero contando grati, CTS y bono</t>
   </si>
   <si>
-    <t xml:space="preserve">Asi queda el ano si usas toda la grati y la CTS en tapar el hueco.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los montos de arriba salen de tu Excel 'Finanzas_personal_1', hoja General, plan 2027.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ojo con tres cifras de ingreso que no coinciden: tus quincenas suman 2,969.94, la formula de AFP da 3,048.50 y tu Excel dice 3,000. Dime cual es la de tu boleta.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grati, CTS y bono no van como ingreso fijo en la app porque no son mensuales: los anotas como Ingreso el mes que caen.</t>
+    <t xml:space="preserve">Asi queda si toda la grati y la CTS van a tapar esto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los gastos salen de tu Excel 'Finanzas_personal_1', hoja General, plan 2027.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El sueldo de octubre de 8,700.74 que estaba en tu Excel no era real: era un tanteo. Aqui va tu neto de siempre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu Excel presupuesta 500 al mes de tarjeta BCP todo 2027. No lo puse: segun la hoja 4 la terminas en diciembre, y eso solo se cumple si dejas de usarla. Los numeros de arriba son el escenario de no volver a usarla.</t>
   </si>
   <si>
     <t xml:space="preserve">8. Para que estas ahorrando</t>
@@ -678,19 +702,25 @@
     <t xml:space="preserve">Para cuando (AAAA-MM-DD)</t>
   </si>
   <si>
+    <t xml:space="preserve">Viaje a Argentina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-11-30</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fondo de emergencia</t>
   </si>
   <si>
     <t xml:space="preserve">2027-12-31</t>
   </si>
   <si>
-    <t xml:space="preserve">Objetivo 5,175 = tres meses de lo que cuesta vivir segun la hoja 7 (1,725 x 3).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ya ahorrado 9,500 = la Caja Huancayo que marcaste como Emergencia en la hoja 2. Estas por encima del objetivo, asi que la app la va a mostrar cumplida: sirve como el piso que no quieres bajar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No le puse mas metas a proposito: con lo que debes hoy, no hay de donde sacar para una meta nueva. Si quieres una igual, dime cual y la agrego.</t>
+    <t xml:space="preserve">Viaje a Argentina: 2,500 para noviembre. El pasaje de 2,500 ya lo pagaste, asi que aqui va solo lo que falta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fondo de emergencia: objetivo 5,175 = tres meses de lo que cuesta vivir (1,725 x 3). Los 9,500 son la Caja Huancayo que marcaste como Emergencia, asi que la app la va a mostrar cumplida: sirve como el piso que no quieres bajar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Wardadito BCP de 1,200 queda como disponible, como pediste.</t>
   </si>
   <si>
     <t xml:space="preserve">El Wardadito BCP de 1,200 lo dejaste en la hoja 2, asi que la app lo va a contar como disponible. Si no quieres verlo asi, avisame y lo saco.</t>
@@ -864,11 +894,15 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -885,11 +919,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -897,11 +931,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -909,11 +943,91 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -921,71 +1035,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="168" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1244,137 +1306,137 @@
   <dimension ref="B2:B33"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="104"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="104"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="3" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="4" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="4" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="4" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="4" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="4" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="3" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="3" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="5" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1397,190 +1459,190 @@
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="11" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="11" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="12" t="n">
         <v>3500</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="11" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="13" t="n">
         <v>0.1</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="11" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="13" t="n">
         <v>0.0155</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="11" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="13" t="n">
         <v>0.0135</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="11" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="12" t="n">
+        <v>78.56</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="11" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="11" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="12" t="n">
         <v>1484.97</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="11" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" s="12" t="n">
         <v>1484.97</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="11" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="11" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="14" t="n">
+      <c r="B18" s="15" t="n">
         <f aca="false">IFERROR(B7-(B7*(B8+B9+B10)+B11),0)</f>
-        <v>3048.5</v>
-      </c>
-      <c r="C18" s="15" t="s">
+        <v>2969.94</v>
+      </c>
+      <c r="C18" s="16" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="14" t="n">
+      <c r="B19" s="15" t="n">
         <f aca="false">IFERROR(B18+B12,0)</f>
-        <v>3048.5</v>
-      </c>
-      <c r="C19" s="15" t="s">
+        <v>2969.94</v>
+      </c>
+      <c r="C19" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1609,211 +1671,211 @@
   <dimension ref="A1:C32"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="12" t="n">
         <v>350</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="10" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="12" t="n">
         <v>238.92</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="10" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="12" t="n">
         <v>108.71</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="10" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="12" t="n">
         <v>1200</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="12" t="n">
         <v>233.84</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="10" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="12" t="n">
         <v>9500</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="11" t="n">
+      <c r="B11" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="10" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="9"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="9"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="9"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="9"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="9"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="9"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="9"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="9"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="9"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="9"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="9"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="9"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="9"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="9"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="9"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="9"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="10"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="10"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="10"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="10"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="10"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="10"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="10"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="10"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="10"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="10"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="10"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="14" t="n">
+      <c r="B28" s="15" t="n">
         <f aca="false">SUM(B5:B27)</f>
         <v>11651.47</v>
       </c>
-      <c r="C28" s="16"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
+      <c r="C28" s="17"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1836,161 +1898,161 @@
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="12" t="n">
         <v>10700</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="9" t="n">
+      <c r="E5" s="12"/>
+      <c r="F5" s="10" t="n">
         <v>1973</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="12" t="n">
         <v>3750</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="D6" s="17" t="n">
-        <v>25</v>
-      </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="9" t="n">
+      <c r="D6" s="18" t="n">
+        <v>31</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="10" t="n">
         <v>141</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="9"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="9"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="9"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="9"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="9"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="9"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="9"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="9"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="10"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="10"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="10"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2013,434 +2075,434 @@
   <dimension ref="A1:H33"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="8" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="20" t="n">
         <v>2750</v>
       </c>
-      <c r="D5" s="20" t="n">
+      <c r="D5" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="E5" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="20" t="n">
+      <c r="F5" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="G5" s="20" t="n">
+      <c r="G5" s="21" t="n">
         <v>2026</v>
       </c>
-      <c r="H5" s="22" t="n">
+      <c r="H5" s="23" t="n">
         <f aca="false">IFERROR(IF(OR($C5="",$D5="",$D5=0),"",IF(N($E5)&gt;0,$C5*((1+$E5)^(1/12)-1)/(1-(1+((1+$E5)^(1/12)-1))^(-$D5)),$C5/$D5)),"")</f>
         <v>2750</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="20" t="n">
         <v>4650</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="21" t="n">
+      <c r="E6" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="21" t="n">
         <v>2026</v>
       </c>
-      <c r="H6" s="22" t="n">
+      <c r="H6" s="23" t="n">
         <f aca="false">IFERROR(IF(OR($C6="",$D6="",$D6=0),"",IF(N($E6)&gt;0,$C6*((1+$E6)^(1/12)-1)/(1-(1+((1+$E6)^(1/12)-1))^(-$D6)),$C6/$D6)),"")</f>
         <v>1550</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="20" t="n">
         <v>413</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="21" t="n">
         <v>2026</v>
       </c>
-      <c r="H7" s="22" t="n">
+      <c r="H7" s="23" t="n">
         <f aca="false">IFERROR(IF(OR($C7="",$D7="",$D7=0),"",IF(N($E7)&gt;0,$C7*((1+$E7)^(1/12)-1)/(1-(1+((1+$E7)^(1/12)-1))^(-$D7)),$C7/$D7)),"")</f>
         <v>413</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="20" t="n">
         <v>2000</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="G8" s="20" t="n">
+      <c r="G8" s="21" t="n">
         <v>2026</v>
       </c>
-      <c r="H8" s="22" t="n">
+      <c r="H8" s="23" t="n">
         <f aca="false">IFERROR(IF(OR($C8="",$D8="",$D8=0),"",IF(N($E8)&gt;0,$C8*((1+$E8)^(1/12)-1)/(1-(1+((1+$E8)^(1/12)-1))^(-$D8)),$C8/$D8)),"")</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="22" t="str">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="23" t="str">
         <f aca="false">IFERROR(IF(OR($C9="",$D9="",$D9=0),"",IF(N($E9)&gt;0,$C9*((1+$E9)^(1/12)-1)/(1-(1+((1+$E9)^(1/12)-1))^(-$D9)),$C9/$D9)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="22" t="str">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="23" t="str">
         <f aca="false">IFERROR(IF(OR($C10="",$D10="",$D10=0),"",IF(N($E10)&gt;0,$C10*((1+$E10)^(1/12)-1)/(1-(1+((1+$E10)^(1/12)-1))^(-$D10)),$C10/$D10)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="22" t="str">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="23" t="str">
         <f aca="false">IFERROR(IF(OR($C11="",$D11="",$D11=0),"",IF(N($E11)&gt;0,$C11*((1+$E11)^(1/12)-1)/(1-(1+((1+$E11)^(1/12)-1))^(-$D11)),$C11/$D11)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="22" t="str">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="23" t="str">
         <f aca="false">IFERROR(IF(OR($C12="",$D12="",$D12=0),"",IF(N($E12)&gt;0,$C12*((1+$E12)^(1/12)-1)/(1-(1+((1+$E12)^(1/12)-1))^(-$D12)),$C12/$D12)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="22" t="str">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="23" t="str">
         <f aca="false">IFERROR(IF(OR($C13="",$D13="",$D13=0),"",IF(N($E13)&gt;0,$C13*((1+$E13)^(1/12)-1)/(1-(1+((1+$E13)^(1/12)-1))^(-$D13)),$C13/$D13)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="22" t="str">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="23" t="str">
         <f aca="false">IFERROR(IF(OR($C14="",$D14="",$D14=0),"",IF(N($E14)&gt;0,$C14*((1+$E14)^(1/12)-1)/(1-(1+((1+$E14)^(1/12)-1))^(-$D14)),$C14/$D14)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="22" t="str">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="23" t="str">
         <f aca="false">IFERROR(IF(OR($C15="",$D15="",$D15=0),"",IF(N($E15)&gt;0,$C15*((1+$E15)^(1/12)-1)/(1-(1+((1+$E15)^(1/12)-1))^(-$D15)),$C15/$D15)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="22" t="str">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="23" t="str">
         <f aca="false">IFERROR(IF(OR($C16="",$D16="",$D16=0),"",IF(N($E16)&gt;0,$C16*((1+$E16)^(1/12)-1)/(1-(1+((1+$E16)^(1/12)-1))^(-$D16)),$C16/$D16)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="22" t="str">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="23" t="str">
         <f aca="false">IFERROR(IF(OR($C17="",$D17="",$D17=0),"",IF(N($E17)&gt;0,$C17*((1+$E17)^(1/12)-1)/(1-(1+((1+$E17)^(1/12)-1))^(-$D17)),$C17/$D17)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="22" t="str">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="23" t="str">
         <f aca="false">IFERROR(IF(OR($C18="",$D18="",$D18=0),"",IF(N($E18)&gt;0,$C18*((1+$E18)^(1/12)-1)/(1-(1+((1+$E18)^(1/12)-1))^(-$D18)),$C18/$D18)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="22" t="str">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="23" t="str">
         <f aca="false">IFERROR(IF(OR($C19="",$D19="",$D19=0),"",IF(N($E19)&gt;0,$C19*((1+$E19)^(1/12)-1)/(1-(1+((1+$E19)^(1/12)-1))^(-$D19)),$C19/$D19)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="22" t="str">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="23" t="str">
         <f aca="false">IFERROR(IF(OR($C20="",$D20="",$D20=0),"",IF(N($E20)&gt;0,$C20*((1+$E20)^(1/12)-1)/(1-(1+((1+$E20)^(1/12)-1))^(-$D20)),$C20/$D20)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="22" t="str">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="23" t="str">
         <f aca="false">IFERROR(IF(OR($C21="",$D21="",$D21=0),"",IF(N($E21)&gt;0,$C21*((1+$E21)^(1/12)-1)/(1-(1+((1+$E21)^(1/12)-1))^(-$D21)),$C21/$D21)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="22" t="str">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="23" t="str">
         <f aca="false">IFERROR(IF(OR($C22="",$D22="",$D22=0),"",IF(N($E22)&gt;0,$C22*((1+$E22)^(1/12)-1)/(1-(1+((1+$E22)^(1/12)-1))^(-$D22)),$C22/$D22)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="22" t="str">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="23" t="str">
         <f aca="false">IFERROR(IF(OR($C23="",$D23="",$D23=0),"",IF(N($E23)&gt;0,$C23*((1+$E23)^(1/12)-1)/(1-(1+((1+$E23)^(1/12)-1))^(-$D23)),$C23/$D23)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="22" t="str">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="23" t="str">
         <f aca="false">IFERROR(IF(OR($C24="",$D24="",$D24=0),"",IF(N($E24)&gt;0,$C24*((1+$E24)^(1/12)-1)/(1-(1+((1+$E24)^(1/12)-1))^(-$D24)),$C24/$D24)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="22" t="str">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="23" t="str">
         <f aca="false">IFERROR(IF(OR($C25="",$D25="",$D25=0),"",IF(N($E25)&gt;0,$C25*((1+$E25)^(1/12)-1)/(1-(1+((1+$E25)^(1/12)-1))^(-$D25)),$C25/$D25)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="22" t="str">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="23" t="str">
         <f aca="false">IFERROR(IF(OR($C26="",$D26="",$D26=0),"",IF(N($E26)&gt;0,$C26*((1+$E26)^(1/12)-1)/(1-(1+((1+$E26)^(1/12)-1))^(-$D26)),$C26/$D26)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="B27" s="16"/>
-      <c r="C27" s="14" t="n">
+      <c r="B27" s="17"/>
+      <c r="C27" s="15" t="n">
         <f aca="false">SUM(C5:C26)</f>
         <v>9813</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="14" t="n">
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="15" t="n">
         <f aca="false">SUM(H5:H26)</f>
         <v>5713</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="s">
         <v>114</v>
       </c>
     </row>
@@ -2463,273 +2525,273 @@
   <dimension ref="A1:G23"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="19" t="n">
+      <c r="B5" s="20" t="n">
         <v>20000</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="20" t="n">
         <v>1200</v>
       </c>
-      <c r="D5" s="20" t="n">
+      <c r="D5" s="21" t="n">
         <v>17</v>
       </c>
-      <c r="E5" s="20" t="n">
+      <c r="E5" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="F5" s="20" t="n">
+      <c r="F5" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="G5" s="20" t="n">
+      <c r="G5" s="21" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="B6" s="19" t="n">
+      <c r="B6" s="20" t="n">
         <v>11500</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="20" t="n">
         <v>447.95</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="21" t="n">
         <v>59</v>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="21" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="20" t="n">
         <v>14500</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="20" t="n">
         <v>534</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="21" t="n">
         <v>58</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="21" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="B8" s="19" t="n">
+      <c r="B8" s="20" t="n">
         <v>2684.56</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="20" t="n">
         <v>266.42</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="G8" s="20" t="n">
+      <c r="G8" s="21" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="20" t="n">
         <v>1000</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="20" t="n">
         <v>210</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="21" t="n">
         <v>29</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="21" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="B19" s="14" t="n">
+      <c r="B19" s="15" t="n">
         <f aca="false">SUM(B5:B18)</f>
         <v>49684.56</v>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C19" s="15" t="n">
         <f aca="false">SUM(C5:C18)</f>
         <v>2658.37</v>
       </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
         <v>125</v>
       </c>
     </row>
@@ -2752,253 +2814,253 @@
   <dimension ref="A1:E32"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="26"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="10" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="10" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="10" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="9"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="9"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="9"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="9"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="9"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="9"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="9"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="9"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="9"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="9"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="9"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="9"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="9"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="9"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="9"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="9"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="9"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="9"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="9"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="10"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="10"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="10"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="10"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="10"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="10"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="10"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="10"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="10"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="10"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B27" s="16"/>
-      <c r="C27" s="14" t="n">
+      <c r="B27" s="17"/>
+      <c r="C27" s="15" t="n">
         <f aca="false">SUM(C5:C26)</f>
         <v>175</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
         <v>141</v>
       </c>
     </row>
@@ -3018,464 +3080,544 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="12" t="n">
         <v>750</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="25" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="25" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>175</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="25" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="25" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="25" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="25" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="25" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="24" t="s">
+      <c r="D12" s="25" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D13" s="25" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="25" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="12" t="n">
         <v>300</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="25" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="25" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="25" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="14" t="n">
+      <c r="B18" s="17"/>
+      <c r="C18" s="15" t="n">
         <f aca="false">SUM(C5:C17)</f>
         <v>1725</v>
       </c>
-      <c r="D18" s="16"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="25" t="s">
+      <c r="D18" s="17"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="26" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="8" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B22" s="22" t="n">
+      <c r="B22" s="23" t="n">
         <f aca="false">IFERROR('1 Perfil'!$B$19*0.5,0)</f>
-        <v>1524.25</v>
-      </c>
-      <c r="C22" s="22" t="n">
+        <v>1484.97</v>
+      </c>
+      <c r="C22" s="23" t="n">
         <f aca="false">SUMIF($B$5:$B$17,"Necesidad",$C$5:$C$17)</f>
         <v>1075</v>
       </c>
-      <c r="D22" s="22" t="n">
+      <c r="D22" s="23" t="n">
         <f aca="false">C22-B22</f>
-        <v>-449.25</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
+        <v>-409.97</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="B23" s="22" t="n">
+      <c r="B23" s="23" t="n">
         <f aca="false">IFERROR('1 Perfil'!$B$19*0.3,0)</f>
-        <v>914.55</v>
-      </c>
-      <c r="C23" s="22" t="n">
+        <v>890.982</v>
+      </c>
+      <c r="C23" s="23" t="n">
         <f aca="false">SUMIF($B$5:$B$17,"Gusto",$C$5:$C$17)</f>
         <v>650</v>
       </c>
-      <c r="D23" s="22" t="n">
+      <c r="D23" s="23" t="n">
         <f aca="false">C23-B23</f>
-        <v>-264.55</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
+        <v>-240.982</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B24" s="22" t="n">
+      <c r="B24" s="23" t="n">
         <f aca="false">IFERROR('1 Perfil'!$B$19*0.2,0)</f>
-        <v>609.7</v>
-      </c>
-      <c r="C24" s="22" t="n">
+        <v>593.988</v>
+      </c>
+      <c r="C24" s="23" t="n">
         <f aca="false">SUMIF($B$5:$B$17,"Ahorro",$C$5:$C$17)+SUMIF($B$5:$B$17,"Deuda",$C$5:$C$17)</f>
         <v>0</v>
       </c>
-      <c r="D24" s="22" t="n">
+      <c r="D24" s="23" t="n">
         <f aca="false">C24-B24</f>
-        <v>-609.7</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+        <v>-593.988</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="26" t="s">
+      <c r="A30" s="27" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="27" t="s">
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="29" t="s">
         <v>130</v>
       </c>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="30" t="s">
         <v>187</v>
       </c>
-      <c r="B32" s="22" t="n">
+      <c r="B32" s="23" t="n">
         <f aca="false">'1 Perfil'!$B$14+'1 Perfil'!$B$15</f>
         <v>2969.94</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="31" t="s">
         <v>188</v>
       </c>
+      <c r="D32" s="28"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="28" t="s">
+      <c r="A33" s="30" t="s">
         <v>189</v>
       </c>
-      <c r="B33" s="22" t="n">
+      <c r="B33" s="23" t="n">
         <f aca="false">$C$18</f>
         <v>1725</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="31" t="s">
         <v>190</v>
       </c>
+      <c r="D33" s="28"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="28" t="s">
+      <c r="A34" s="30" t="s">
         <v>191</v>
       </c>
-      <c r="B34" s="22" t="n">
+      <c r="B34" s="23" t="n">
         <f aca="false">'4 Cuotas tarjeta'!$H$27</f>
         <v>5713</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="31" t="s">
         <v>192</v>
       </c>
+      <c r="D34" s="28"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="28" t="s">
+      <c r="A35" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="B35" s="22" t="n">
+      <c r="B35" s="23" t="n">
         <f aca="false">'5 Prestamos'!$C$19</f>
         <v>2658.37</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="31" t="s">
         <v>194</v>
       </c>
+      <c r="D35" s="28"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="B36" s="29" t="n">
+      <c r="B36" s="32" t="n">
         <f aca="false">B33+B34+B35</f>
         <v>10096.37</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="31" t="s">
         <v>196</v>
       </c>
+      <c r="D36" s="28"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="13" t="s">
+      <c r="A37" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="B37" s="30" t="n">
+      <c r="B37" s="33" t="n">
         <f aca="false">B32-B36</f>
         <v>-7126.43</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="31" t="s">
         <v>198</v>
       </c>
+      <c r="D37" s="28"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="30" t="s">
         <v>199</v>
       </c>
-      <c r="B38" s="29" t="n">
+      <c r="B38" s="23" t="n">
+        <v>2550</v>
+      </c>
+      <c r="C38" s="31" t="s">
+        <v>200</v>
+      </c>
+      <c r="D38" s="28"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="B39" s="23" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="D39" s="28"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="B40" s="32" t="n">
+        <f aca="false">B33+B38+B35+B39</f>
+        <v>9433.37</v>
+      </c>
+      <c r="C40" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="D40" s="28"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="B41" s="33" t="n">
+        <f aca="false">B32-B40</f>
+        <v>-6463.43</v>
+      </c>
+      <c r="C41" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="D41" s="28"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="B42" s="35" t="n">
         <f aca="false">B33+B35</f>
         <v>4383.37</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="B39" s="30" t="n">
-        <f aca="false">B32-B38</f>
+      <c r="C42" s="36" t="s">
+        <v>208</v>
+      </c>
+      <c r="D42" s="28"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="B43" s="37" t="n">
+        <f aca="false">B32-B42</f>
         <v>-1413.43</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="B40" s="22" t="n">
+      <c r="C43" s="36" t="s">
+        <v>210</v>
+      </c>
+      <c r="D43" s="28"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="B44" s="38" t="n">
         <f aca="false">14000/12</f>
         <v>1166.66666666667</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="B41" s="30" t="n">
-        <f aca="false">B39+B40</f>
+      <c r="C44" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="D44" s="28"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="B45" s="37" t="n">
+        <f aca="false">B43+B44</f>
         <v>-246.763333333333</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="s">
-        <v>209</v>
-      </c>
+      <c r="C45" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="D45" s="28"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="28"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3496,133 +3638,141 @@
   <dimension ref="A1:D22"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>211</v>
+      <c r="A1" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="B5" s="11" t="n">
+      <c r="A4" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="B6" s="12" t="n">
         <v>5175</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>9500</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="9"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="9"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="9"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="9"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="9"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="9"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="9"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="9"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="9"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="9"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="9"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>221</v>
+      <c r="D6" s="10" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="10"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="10"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="10"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="10"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>231</v>
       </c>
     </row>
   </sheetData>
